--- a/data/trans_orig/IP1022_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23973</t>
+          <t>24091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>31280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>53893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50950</t>
+          <t>50211</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59610</t>
+          <t>59283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85124</t>
+          <t>85402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110654</t>
+          <t>110587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16936</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33965</t>
+          <t>34689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>24833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54193</t>
+          <t>55766</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47038</t>
+          <t>46411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80441</t>
+          <t>83065</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425121</t>
+          <t>424397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442150</t>
+          <t>442087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458190</t>
+          <t>456617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487482</t>
+          <t>487550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>891028</t>
+          <t>888404</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>924431</t>
+          <t>925058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25171</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38654</t>
+          <t>37675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130821</t>
+          <t>132201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142854</t>
+          <t>142919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158178</t>
+          <t>158191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173477</t>
+          <t>173496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>294246</t>
+          <t>295225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>313150</t>
+          <t>312942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31833</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63484</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79980</t>
+          <t>78467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83615</t>
+          <t>83407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130260</t>
+          <t>130168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>599831</t>
+          <t>598316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>631482</t>
+          <t>630909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>677756</t>
+          <t>679269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>712282</t>
+          <t>713705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1290791</t>
+          <t>1290883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1337436</t>
+          <t>1337644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1022_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1022_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5290</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9666</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7391</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24091</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51442</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47066</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54522</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>47287</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30587</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53893</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>86,48%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56160</t>
+          <t>44442</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50211</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59283</t>
+          <t>46097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>103447</t>
+          <t>95885</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85402</t>
+          <t>90251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110587</t>
+          <t>99423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27875</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19404</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37816</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>25113</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16999</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34689</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35227</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24833</t>
+          <t>18802</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55766</t>
+          <t>35861</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>60340</t>
+          <t>54070</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46411</t>
+          <t>43384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83065</t>
+          <t>67307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>443434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>433493</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>451905</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>604</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>433973</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>424397</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>442087</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>477156</t>
+          <t>404737</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>456617</t>
+          <t>395071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487550</t>
+          <t>412130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>911129</t>
+          <t>848171</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>888404</t>
+          <t>834934</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925058</t>
+          <t>858857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>471309</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>471309</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>471309</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459086</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459086</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459086</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512383</t>
+          <t>430932</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512383</t>
+          <t>430932</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512383</t>
+          <t>430932</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>971469</t>
+          <t>902241</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>971469</t>
+          <t>902241</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>971469</t>
+          <t>902241</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15861</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10335</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25362</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11300</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6632</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17350</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>18641</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27857</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37675</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152558</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>143057</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158084</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>138251</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>132201</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>142919</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166792</t>
+          <t>138180</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158191</t>
+          <t>131335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>173496</t>
+          <t>142927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>305043</t>
+          <t>290738</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295225</t>
+          <t>280221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>312942</t>
+          <t>298581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>49026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38275</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>63224</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>43804</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32406</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>64999</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>40307</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30664</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>51401</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>4,89%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>57628</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>44031</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>78467</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>89332</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83407</t>
+          <t>75922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130168</t>
+          <t>107338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1862,74 +1862,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>647434</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>633236</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>658185</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>883</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>619511</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>598316</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>630909</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>587359</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>576265</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>597002</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>91,81%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>95,11%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>700108</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>679269</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>713705</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,64%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1791</t>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1319619</t>
+          <t>1234794</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1290883</t>
+          <t>1216788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1337644</t>
+          <t>1248204</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>696460</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663315</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663315</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>627666</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>627666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>757736</t>
+          <t>627666</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1421051</t>
+          <t>1324126</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1421051</t>
+          <t>1324126</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1421051</t>
+          <t>1324126</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
